--- a/00-notes/literature-review.xlsx
+++ b/00-notes/literature-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifpenfr-my.sharepoint.com/personal/romain_capliez_ifpen_fr/Documents/Documents/2026-mineral-oil-macro-impact/00-notes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projets\2026-mineral-oil-macro-impact\00-notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{804047E6-7AF2-48A4-A0A6-8091DD39D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{194A7609-12DE-49BF-94BF-CDD9DB03B253}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C915BD9F-97A5-4430-B41F-56445FA1E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Problématique</t>
   </si>
@@ -148,6 +148,110 @@
   </si>
   <si>
     <t>Exposure measure ; Conclusions et explication intéresante</t>
+  </si>
+  <si>
+    <t>Atakhanova2020</t>
+  </si>
+  <si>
+    <t>Metal intensity of use in the era of global value chains</t>
+  </si>
+  <si>
+    <t>Study metal intensity of use trough the value added</t>
+  </si>
+  <si>
+    <t>Panel analysis</t>
+  </si>
+  <si>
+    <t>TiVA : allows for the measurement of value added of a particular industry embodied in final demand, while accounting for contributions of domeestic and foreign suppliers of intermediate goods.
+Metal intensity : ratio of value added of metal consumed to the aggregate value added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic structure explains variations in metal intensity. Given the declining share of manufacturing and increasing shares of services in both advanced and developing economies, we may expect global metal intensity of tuse to decrease in the long run. However, metal intensity of use may receive some boost due to expansionary stages of the business cycle and increased investment. In addition, those metals that are used in high technology applications may experience increasing intensity of use. </t>
+  </si>
+  <si>
+    <t>Mesure d'intensité métallique à travers la valeur ajoutée pour éviterr les doubles contages</t>
+  </si>
+  <si>
+    <t>Cunado2015</t>
+  </si>
+  <si>
+    <t>Macroeconomic impacts of oil price shocks in Asian economies</t>
+  </si>
+  <si>
+    <t>Analyze the macroeconomic impact of structural oil shocks in four of the top oil-consuming Asian economies.</t>
+  </si>
+  <si>
+    <t>SVAR sign restrictions on oil market variables only</t>
+  </si>
+  <si>
+    <t>1997Q2:2014Q3 ; World oil production ; Real price of crude oil ; Real world economic activity proxy ; Real GDP Consumer prrice ; real exchange rate ; Discount rate ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil supply shocks has limited impacts reflecting structural chanfes of the economies
+Notable positive responses of GDP to an oil demand shock driven by economic activity
+CPIs in India and Indonesia remain fairly stable upon the arrival of all three oil shocks, likely due to the energy price regulation and government subsidization.
+Oil specific demand shock has differential efects depending on a country's position in the global oil market, with Indonesia, a previous net-oil exporter, being the only country with mild but positive responses of GDP. </t>
+  </si>
+  <si>
+    <t>Similaire à ce que je veux faire (4 variables macro étudiées). Revue sur les impacts macro du pétrole</t>
+  </si>
+  <si>
+    <t>The effect of oil supply shocks on US economic activity: What have we learned?</t>
+  </si>
+  <si>
+    <t>Herrera2020</t>
+  </si>
+  <si>
+    <t>Investigate how the response of US GDP to oil shocks vary depending of the identification scheme</t>
+  </si>
+  <si>
+    <t>SVAR (4 identification scheme) for oil marketHerrera
+OLS : response of GDP to strcutural shocks from VAR (oil markets only)</t>
+  </si>
+  <si>
+    <t>Most variations of US GDP and oil prices to oil supply disruptions is attributable to differences in identification assumptions and estimation techniques.
+Models that impose a large short-run price elasticity of oil supply imply a larger response of oil prices and a larger longer-lived contraction in US real GDP
+If we condition on a range of supply elasticity values suppoted by microeconomic estimates, the differences in the oil prrice responses diminishes.</t>
+  </si>
+  <si>
+    <t>Methodologie en 2 étapes similairer à ce que je veux (estimer le choc puis régression). Montre l'importance des différents schéma d'identification</t>
+  </si>
+  <si>
+    <t>Karacan2021</t>
+  </si>
+  <si>
+    <t>The impact of oil price on transition toward renewable energy consumption? Evidence from Russia</t>
+  </si>
+  <si>
+    <t>Investigates the impact of oil price, income and carbon dioaxide emissions on renewable energy consumption in Russia.</t>
+  </si>
+  <si>
+    <t>VECM</t>
+  </si>
+  <si>
+    <t>Oil price affects rrenewable energy consumption negatively -&gt; slows the transition from conventional to rrenewable energy sources.
+Real GDP has a positive influence on renewable energy consumption.</t>
+  </si>
+  <si>
+    <t>Mukhtarov2020</t>
+  </si>
+  <si>
+    <t>Do high oil prices obstruct the transition to renewable energy consumption?</t>
+  </si>
+  <si>
+    <t>Analyzes the impact of economic growth, carbon dioxide emissions and oil price on renewable enerrgy consumption</t>
+  </si>
+  <si>
+    <t>ARDL, Cointegrration</t>
+  </si>
+  <si>
+    <t>Azerbaijan 1992-2015</t>
+  </si>
+  <si>
+    <t>Russia 1990-2015</t>
+  </si>
+  <si>
+    <t>There is a lonng-run positive and statistically significant effect of economic growth on rrernewable energy consumption and a negative impact of oil price</t>
   </si>
 </sst>
 </file>
@@ -171,7 +275,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,7 +296,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +352,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="2" customWidth="1"/>
@@ -600,47 +722,154 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/00-notes/literature-review.xlsx
+++ b/00-notes/literature-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projets\2026-mineral-oil-macro-impact\00-notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifpenfr-my.sharepoint.com/personal/romain_capliez_ifpen_fr/Documents/Documents/2026-mineral-oil-macro-impact/00-notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C915BD9F-97A5-4430-B41F-56445FA1E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{C915BD9F-97A5-4430-B41F-56445FA1E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B415BB-58B4-4DC0-A5C6-67E7589044D6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Problématique</t>
   </si>
@@ -252,6 +252,97 @@
   </si>
   <si>
     <t>There is a lonng-run positive and statistically significant effect of economic growth on rrernewable energy consumption and a negative impact of oil price</t>
+  </si>
+  <si>
+    <t>Alessandri2025</t>
+  </si>
+  <si>
+    <t>Natural gas and the macroeconomy: Not all enegry shocks are alike</t>
+  </si>
+  <si>
+    <t>How do shocks to the supply of natural gas affect output and inflation?</t>
+  </si>
+  <si>
+    <t>Seasonnally adjutsment of prices with Census X13
+VAR with instrumental variable for gas prices
+Instrument using daily news on the European gas market for gas supplshocks: Extract news about supply changes an compute the daoly change in prices at these dates and 0 otherwise.</t>
+  </si>
+  <si>
+    <t>Montlhy data
+Gas prices ; energy consumer prices (month to month inflation rate) ; core consumer prices mont to month inflation rate) ; industrial production ; stock prices (Eurostoxx 600 equity index); shadow short term rate (monetary policy short term rate computed by Krippner 2013) ; 10 year Bund rate
+energy producer price index ; HICP transportation fuels component ; price of electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative supply shocks have sizable stagflationary effects and account for nearly 50% of the increase in core prices observed between 2021 and 2023 -&gt; a 10% increase in gas prices lea to a 0.5% increase in core prices. 
+The propagation to core prices appears to be larger compared to oil shocks, suggesting that the structural differences between the two markets matter from an aggregate perspective.
+A given shift in energy hicp may trigger a more gradual but ultimately stronger response if and when it originates in the gas market. </t>
+  </si>
+  <si>
+    <t>Méthodo très bien (et similaire à ce que je veux faire) + méthode d'instrument + résultats intéressants</t>
+  </si>
+  <si>
+    <t>Considine2023</t>
+  </si>
+  <si>
+    <t>The effect of a shock to critical minerals prices on the world oil price and inflation</t>
+  </si>
+  <si>
+    <t>Examine the consequences of market disturbances from Cm price shocks on major global and country-specific macroeconomic indicators.</t>
+  </si>
+  <si>
+    <t>GVAR</t>
+  </si>
+  <si>
+    <t>Critical mineral price index of U.S. Bureau of Labor Statistics 2022</t>
+  </si>
+  <si>
+    <t>Survey of litterature concerning what has been studied between Critical metal prices and the macroeconomic variables.
+Survey of literrature using the GVAR methodology</t>
+  </si>
+  <si>
+    <t>Résultats sur le sujet</t>
+  </si>
+  <si>
+    <t>Su2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rise of green energy metal: could lithium threaten the status of oil </t>
+  </si>
+  <si>
+    <t>Explore the correlation between the oil and lithium markets</t>
+  </si>
+  <si>
+    <t>Granger causality tests</t>
+  </si>
+  <si>
+    <t>OIl prices, lithium prices</t>
+  </si>
+  <si>
+    <t>High oil prices increases the lithium demand and its prices through taking new energy vehicles as a substitue for conventional automobile, indicating that lithium may threaten the status of oil under te oil bull market.
+But this is not supported under the oil bear market, low oil price lessens the attraction of new enegy vehicles and then reduces lithium demand and price.</t>
+  </si>
+  <si>
+    <t>Casoli2024</t>
+  </si>
+  <si>
+    <t>Energy shocks in the Euro area: Disentangling the pass-through from oil and gas prices to inflation</t>
+  </si>
+  <si>
+    <t>Study the relationship between different energy shocks and inflation dynamics in Europe</t>
+  </si>
+  <si>
+    <t>Bayesian SVAR</t>
+  </si>
+  <si>
+    <t>Global oil production ; global oil real price ; global oil inventories ; global economic activities ; European natural gas supply ; European gas price ; European gas inventories ; European economic activity ; Expected inflation rate ; inflation rate</t>
+  </si>
+  <si>
+    <t>Since the post-pandemic recovery, inflation in the Euro area is mostly driven by energy price shocks and aggregate supply factors. In particular, the high peaks of the Eurozone are mostly associated with natural gas supply shocks.
+The responses of expected and headline inflation to energy supply and consumption demand shocks are relevant and persistent after more than one year
+Oil and gas speculative demand shocks are rapidly absorbed, while economic activity shocks cause a rise in both inflation rates but the effect is smaller if compared to energy shocks</t>
+  </si>
+  <si>
+    <t>Résultats sur le gas et le pétrole</t>
   </si>
 </sst>
 </file>
@@ -275,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -312,6 +403,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -340,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -358,6 +455,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="2" customWidth="1"/>
@@ -872,6 +975,96 @@
         <v>65</v>
       </c>
     </row>
+    <row r="11" spans="1:7" ht="165" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
